--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -387,7 +387,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -521,7 +521,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -550,7 +550,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -624,7 +624,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -655,7 +655,7 @@
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -927,7 +927,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -990,7 +990,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1018,7 +1018,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1038,7 +1038,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1120,7 +1120,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1191,7 +1191,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1220,7 +1220,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1268,7 +1268,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1298,7 +1298,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1310,7 +1310,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1335,7 +1335,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1410,7 +1410,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1460,7 +1460,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1493,7 +1493,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1530,7 +1530,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1993,7 +1993,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="175.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2008,7 +2008,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -387,7 +387,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -521,7 +521,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -550,7 +550,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Radiology)
 </t>
   </si>
   <si>
@@ -624,7 +624,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -655,7 +655,7 @@
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -927,7 +927,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -990,7 +990,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1018,7 +1018,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1038,7 +1038,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1120,7 +1120,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1191,7 +1191,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1220,7 +1220,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1268,7 +1268,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1298,7 +1298,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1310,7 +1310,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1335,7 +1335,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1410,7 +1410,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1460,7 +1460,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1493,7 +1493,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1530,7 +1530,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
 </t>
   </si>
   <si>
@@ -1993,7 +1993,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="175.3828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2008,7 +2008,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.62109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
